--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_28-01-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_28-01-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="142">
   <si>
     <t>SKU</t>
   </si>
@@ -202,9 +202,6 @@
     <t>£41.67</t>
   </si>
   <si>
-    <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
-  </si>
-  <si>
     <t>£18.75</t>
   </si>
   <si>
@@ -250,7 +247,46 @@
     <t>£77.34</t>
   </si>
   <si>
-    <t>Error: list index out of range</t>
+    <t>£14.54ex.</t>
+  </si>
+  <si>
+    <t>£17.48ex.</t>
+  </si>
+  <si>
+    <t>£18.94ex.</t>
+  </si>
+  <si>
+    <t>£23.24ex.</t>
+  </si>
+  <si>
+    <t>£26.16ex.</t>
+  </si>
+  <si>
+    <t>£27.24ex.</t>
+  </si>
+  <si>
+    <t>£29.17ex.</t>
+  </si>
+  <si>
+    <t>£32.49ex.</t>
+  </si>
+  <si>
+    <t>£34.56ex.</t>
+  </si>
+  <si>
+    <t>£38.66ex.</t>
+  </si>
+  <si>
+    <t>£41.91ex.</t>
+  </si>
+  <si>
+    <t>£48.35ex.</t>
+  </si>
+  <si>
+    <t>£50.21ex.</t>
+  </si>
+  <si>
+    <t>£50.55ex.</t>
   </si>
   <si>
     <t>£12.25</t>
@@ -825,31 +861,31 @@
         <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
         <v>56</v>
       </c>
       <c r="H2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="K2" t="s">
         <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M2" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -869,31 +905,31 @@
         <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H3" t="s">
         <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="J3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
         <v>56</v>
       </c>
       <c r="L3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -913,31 +949,31 @@
         <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
         <v>78</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I4" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J4" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="K4" t="s">
         <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M4" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N4" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -957,31 +993,31 @@
         <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I5" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="J5" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="K5" t="s">
         <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M5" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N5" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1001,31 +1037,31 @@
         <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I6" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="J6" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="K6" t="s">
         <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M6" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N6" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1045,31 +1081,31 @@
         <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H7" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="J7" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="K7" t="s">
         <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M7" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N7" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1089,31 +1125,31 @@
         <v>52</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="J8" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="K8" t="s">
         <v>56</v>
       </c>
       <c r="L8" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N8" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1130,34 +1166,34 @@
         <v>53</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s">
         <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="J9" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="K9" t="s">
         <v>56</v>
       </c>
       <c r="L9" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M9" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N9" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1177,31 +1213,31 @@
         <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I10" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="J10" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="K10" t="s">
         <v>56</v>
       </c>
       <c r="L10" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M10" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N10" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1221,31 +1257,31 @@
         <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I11" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="J11" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="K11" t="s">
         <v>56</v>
       </c>
       <c r="L11" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M11" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N11" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1265,31 +1301,31 @@
         <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s">
         <v>56</v>
       </c>
       <c r="I12" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J12" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="K12" t="s">
         <v>56</v>
       </c>
       <c r="L12" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M12" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N12" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1309,31 +1345,31 @@
         <v>57</v>
       </c>
       <c r="F13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I13" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="J13" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="K13" t="s">
         <v>56</v>
       </c>
       <c r="L13" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M13" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N13" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1365,16 +1401,16 @@
         <v>56</v>
       </c>
       <c r="J14" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="K14" t="s">
         <v>56</v>
       </c>
       <c r="L14" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M14" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N14" t="s">
         <v>56</v>
@@ -1397,31 +1433,31 @@
         <v>59</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s">
         <v>56</v>
       </c>
       <c r="I15" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="J15" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="K15" t="s">
         <v>56</v>
       </c>
       <c r="L15" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N15" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1441,31 +1477,31 @@
         <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s">
         <v>56</v>
       </c>
       <c r="I16" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="J16" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="K16" t="s">
         <v>56</v>
       </c>
       <c r="L16" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M16" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N16" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1485,31 +1521,31 @@
         <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I17" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="J17" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="K17" t="s">
         <v>56</v>
       </c>
       <c r="L17" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M17" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N17" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_28-01-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_28-01-2026.xlsx
@@ -247,46 +247,46 @@
     <t>£77.34</t>
   </si>
   <si>
-    <t>£14.54ex.</t>
-  </si>
-  <si>
-    <t>£17.48ex.</t>
-  </si>
-  <si>
-    <t>£18.94ex.</t>
-  </si>
-  <si>
-    <t>£23.24ex.</t>
-  </si>
-  <si>
-    <t>£26.16ex.</t>
-  </si>
-  <si>
-    <t>£27.24ex.</t>
-  </si>
-  <si>
-    <t>£29.17ex.</t>
-  </si>
-  <si>
-    <t>£32.49ex.</t>
-  </si>
-  <si>
-    <t>£34.56ex.</t>
-  </si>
-  <si>
-    <t>£38.66ex.</t>
-  </si>
-  <si>
-    <t>£41.91ex.</t>
-  </si>
-  <si>
-    <t>£48.35ex.</t>
-  </si>
-  <si>
-    <t>£50.21ex.</t>
-  </si>
-  <si>
-    <t>£50.55ex.</t>
+    <t>£14.54</t>
+  </si>
+  <si>
+    <t>£17.48</t>
+  </si>
+  <si>
+    <t>£18.94</t>
+  </si>
+  <si>
+    <t>£23.24</t>
+  </si>
+  <si>
+    <t>£26.16</t>
+  </si>
+  <si>
+    <t>£27.24</t>
+  </si>
+  <si>
+    <t>£29.17</t>
+  </si>
+  <si>
+    <t>£32.49</t>
+  </si>
+  <si>
+    <t>£34.56</t>
+  </si>
+  <si>
+    <t>£38.66</t>
+  </si>
+  <si>
+    <t>£41.91</t>
+  </si>
+  <si>
+    <t>£48.35</t>
+  </si>
+  <si>
+    <t>£50.21</t>
+  </si>
+  <si>
+    <t>£50.55</t>
   </si>
   <si>
     <t>£12.25</t>
@@ -397,7 +397,7 @@
     <t>POA</t>
   </si>
   <si>
-    <t>£14.54</t>
+    <t>Error: HTTPConnectionPool(host='localhost', port=53653): Read timed out. (read timeout=120)</t>
   </si>
   <si>
     <t>£19.36</t>
